--- a/Lab_Data/Unsat Lab.xlsx
+++ b/Lab_Data/Unsat Lab.xlsx
@@ -1,13 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diama\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6AF92-422D-4BCC-9956-8E893CB0B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Infiltration" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Evaporation" sheetId="2" r:id="rId6"/>
+    <sheet name="Procedure Testing" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -125,24 +146,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -153,7 +176,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -163,47 +186,44 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -393,42 +413,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A2:N27"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="26.0"/>
-    <col customWidth="1" min="3" max="3" width="20.5"/>
-    <col customWidth="1" min="4" max="4" width="23.0"/>
-    <col customWidth="1" min="5" max="5" width="18.63"/>
-    <col customWidth="1" min="8" max="8" width="16.5"/>
-    <col customWidth="1" min="13" max="13" width="18.38"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -455,7 +467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
@@ -466,29 +478,29 @@
         <v>70.56</v>
       </c>
       <c r="E4" s="1">
-        <v>261.47</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" ref="F4:F7" si="1">E4-D4</f>
-        <v>190.91</v>
+        <v>261.47000000000003</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F7" si="0">E4-D4</f>
+        <v>190.91000000000003</v>
       </c>
       <c r="G4" s="1">
         <v>343.52</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <f>G4-C17</f>
-        <v>256.65</v>
-      </c>
-      <c r="I4" s="2">
-        <f t="shared" ref="I4:I7" si="2">H4</f>
-        <v>256.65</v>
-      </c>
-      <c r="J4" s="2">
+        <v>256.64999999999998</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" ref="I4:I7" si="1">H4</f>
+        <v>256.64999999999998</v>
+      </c>
+      <c r="J4" s="1">
         <f>I4/60</f>
-        <v>4.2775</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4.2774999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -501,23 +513,23 @@
       <c r="E5" s="1">
         <v>208.28</v>
       </c>
-      <c r="F5" s="2">
-        <f t="shared" si="1"/>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
         <v>178.41</v>
       </c>
       <c r="G5" s="1">
         <v>252.94</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <f>G5-E5</f>
         <v>44.66</v>
       </c>
-      <c r="I5" s="2">
-        <f t="shared" si="2"/>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
         <v>44.66</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -530,27 +542,27 @@
       <c r="E6" s="1">
         <v>212.04</v>
       </c>
-      <c r="F6" s="2">
-        <f t="shared" si="1"/>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
         <v>84.32</v>
       </c>
       <c r="G6" s="1">
         <v>307.7</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <f>G6-C16</f>
         <v>220.74</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" si="2"/>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
         <v>220.74</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <f>I6/60</f>
-        <v>3.679</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>3.6790000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
@@ -558,28 +570,28 @@
         <v>13</v>
       </c>
       <c r="D7" s="1">
-        <v>68.51</v>
+        <v>68.510000000000005</v>
       </c>
       <c r="E7" s="1">
         <v>158.49</v>
       </c>
-      <c r="F7" s="2">
-        <f t="shared" si="1"/>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
         <v>89.98</v>
       </c>
       <c r="G7" s="1">
         <v>182.22</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <f>G7-E7</f>
-        <v>23.73</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="2"/>
-        <v>23.73</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>23.72999999999999</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="1"/>
+        <v>23.72999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -587,7 +599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -595,12 +607,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E15" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
@@ -635,7 +655,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" s="1">
         <v>86.87</v>
       </c>
@@ -649,28 +669,28 @@
         <v>70.56</v>
       </c>
       <c r="H17" s="1">
-        <v>261.47</v>
-      </c>
-      <c r="I17" s="2">
-        <f t="shared" ref="I17:I18" si="3">H17-G17</f>
-        <v>190.91</v>
+        <v>261.47000000000003</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" ref="I17:I18" si="2">H17-G17</f>
+        <v>190.91000000000003</v>
       </c>
       <c r="J17" s="1">
         <v>86.87</v>
       </c>
       <c r="K17" s="1">
-        <v>256.65</v>
-      </c>
-      <c r="L17" s="2">
-        <f t="shared" ref="L17:L19" si="4">K17</f>
-        <v>256.65</v>
-      </c>
-      <c r="M17" s="2">
-        <f t="shared" ref="M17:M18" si="5">L17/60</f>
-        <v>4.2775</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>256.64999999999998</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" ref="L17:L19" si="3">K17</f>
+        <v>256.64999999999998</v>
+      </c>
+      <c r="M17" s="1">
+        <f t="shared" ref="M17:M18" si="4">L17/60</f>
+        <v>4.2774999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E18" s="1" t="s">
         <v>12</v>
       </c>
@@ -683,8 +703,8 @@
       <c r="H18" s="1">
         <v>212.04</v>
       </c>
-      <c r="I18" s="2">
-        <f t="shared" si="3"/>
+      <c r="I18" s="1">
+        <f t="shared" si="2"/>
         <v>84.32</v>
       </c>
       <c r="J18" s="1">
@@ -693,30 +713,38 @@
       <c r="K18" s="1">
         <v>220.74</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="1">
+        <f t="shared" si="3"/>
+        <v>220.74</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="4"/>
-        <v>220.74</v>
-      </c>
-      <c r="M18" s="2">
-        <f t="shared" si="5"/>
-        <v>3.679</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="L19" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
+        <v>3.6790000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="L19" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
       <c r="N20" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E21" s="1" t="s">
         <v>1</v>
       </c>
@@ -748,7 +776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E22" s="1" t="s">
         <v>11</v>
       </c>
@@ -761,30 +789,30 @@
       <c r="H22" s="1">
         <v>208.28</v>
       </c>
-      <c r="I22" s="2">
-        <f t="shared" ref="I22:I23" si="6">H22-G22</f>
+      <c r="I22" s="1">
+        <f t="shared" ref="I22:I23" si="5">H22-G22</f>
         <v>178.41</v>
       </c>
       <c r="J22" s="1">
         <v>252.94</v>
       </c>
-      <c r="K22" s="2">
-        <f t="shared" ref="K22:K23" si="7">J22-H22</f>
+      <c r="K22" s="1">
+        <f t="shared" ref="K22:K23" si="6">J22-H22</f>
         <v>44.66</v>
       </c>
-      <c r="L22" s="2">
-        <f t="shared" ref="L22:L23" si="8">K22</f>
+      <c r="L22" s="1">
+        <f t="shared" ref="L22:L23" si="7">K22</f>
         <v>44.66</v>
       </c>
       <c r="M22" s="1">
         <v>224.08</v>
       </c>
-      <c r="N22" s="2">
-        <f t="shared" ref="N22:N23" si="9">J22-M22</f>
-        <v>28.86</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="N22" s="1">
+        <f t="shared" ref="N22:N23" si="8">J22-M22</f>
+        <v>28.859999999999985</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E23" s="1" t="s">
         <v>14</v>
       </c>
@@ -792,66 +820,66 @@
         <v>13</v>
       </c>
       <c r="G23" s="1">
-        <v>68.51</v>
+        <v>68.510000000000005</v>
       </c>
       <c r="H23" s="1">
         <v>158.49</v>
       </c>
-      <c r="I23" s="2">
-        <f t="shared" si="6"/>
+      <c r="I23" s="1">
+        <f t="shared" si="5"/>
         <v>89.98</v>
       </c>
       <c r="J23" s="1">
         <v>182.22</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="1">
+        <f t="shared" si="6"/>
+        <v>23.72999999999999</v>
+      </c>
+      <c r="L23" s="1">
         <f t="shared" si="7"/>
-        <v>23.73</v>
-      </c>
-      <c r="L23" s="2">
-        <f t="shared" si="8"/>
-        <v>23.73</v>
+        <v>23.72999999999999</v>
       </c>
       <c r="M23" s="1">
         <v>158.18</v>
       </c>
-      <c r="N23" s="2">
-        <f t="shared" si="9"/>
-        <v>24.04</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="N23" s="1">
+        <f t="shared" si="8"/>
+        <v>24.039999999999992</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="L24" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M24" s="1">
         <v>206.84</v>
       </c>
-      <c r="N24" s="2">
-        <f t="shared" ref="N24:N25" si="10">J22-M24</f>
-        <v>46.1</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="N24" s="1">
+        <f t="shared" ref="N24:N25" si="9">J22-M24</f>
+        <v>46.099999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M25" s="1">
-        <v>157.23</v>
-      </c>
-      <c r="N25" s="2">
-        <f t="shared" si="10"/>
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>157.22999999999999</v>
+      </c>
+      <c r="N25" s="1">
+        <f t="shared" si="9"/>
+        <v>24.990000000000009</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="L26" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27">
-      <c r="L27" s="4">
-        <v>46108.0</v>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="L27" s="2">
+        <v>46108</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>35</v>
@@ -862,6 +890,6 @@
     <mergeCell ref="E15:M15"/>
     <mergeCell ref="E20:M20"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>